--- a/010-npm_node/02-results/2211AM01S Fairmount Signage REV 1.xlsx
+++ b/010-npm_node/02-results/2211AM01S Fairmount Signage REV 1.xlsx
@@ -464,7 +464,7 @@
         <v>CONTACT</v>
       </c>
       <c r="I2" t="str">
-        <v>CONTRACT_NUMBER</v>
+        <v>CONTRACT</v>
       </c>
       <c r="J2" t="str">
         <v>REVISIONS</v>
@@ -476,7 +476,7 @@
         <v>CONTRACT_FILE</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -504,8 +504,9 @@
       <c r="I3" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J3" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J3" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K3" t="str">
         <v>AM FAIRMOUNT</v>
@@ -514,7 +515,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -542,8 +543,9 @@
       <c r="I4" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J4" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J4" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K4" t="str">
         <v>AM FAIRMOUNT</v>
@@ -552,7 +554,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -580,8 +582,9 @@
       <c r="I5" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J5" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J5" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K5" t="str">
         <v>AM FAIRMOUNT</v>
@@ -590,7 +593,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -618,8 +621,9 @@
       <c r="I6" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J6" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J6" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K6" t="str">
         <v>AM FAIRMOUNT</v>
@@ -628,7 +632,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>#1: ENTRY SIGNAGE</v>
       </c>
@@ -656,8 +660,9 @@
       <c r="I7" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J7" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J7" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K7" t="str">
         <v>AM FAIRMOUNT</v>
@@ -666,7 +671,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" xml:space="preserve">
       <c r="A8" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -694,8 +699,9 @@
       <c r="I8" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J8" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J8" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K8" t="str">
         <v>AM FAIRMOUNT</v>
@@ -704,7 +710,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" xml:space="preserve">
       <c r="A9" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -732,8 +738,9 @@
       <c r="I9" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J9" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J9" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K9" t="str">
         <v>AM FAIRMOUNT</v>
@@ -742,7 +749,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -770,8 +777,9 @@
       <c r="I10" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J10" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J10" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K10" t="str">
         <v>AM FAIRMOUNT</v>
@@ -780,7 +788,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" xml:space="preserve">
       <c r="A11" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -808,8 +816,9 @@
       <c r="I11" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J11" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J11" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K11" t="str">
         <v>AM FAIRMOUNT</v>
@@ -818,7 +827,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -846,8 +855,9 @@
       <c r="I12" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J12" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J12" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K12" t="str">
         <v>AM FAIRMOUNT</v>
@@ -856,7 +866,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>#2: LEASING CENTER- EXTERIOR SIGNAGE</v>
       </c>
@@ -884,8 +894,9 @@
       <c r="I13" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J13" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J13" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K13" t="str">
         <v>AM FAIRMOUNT</v>
@@ -894,7 +905,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" xml:space="preserve">
       <c r="A14" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -922,8 +933,9 @@
       <c r="I14" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J14" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K14" t="str">
         <v>AM FAIRMOUNT</v>
@@ -932,7 +944,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" xml:space="preserve">
       <c r="A15" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -960,8 +972,9 @@
       <c r="I15" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J15" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J15" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K15" t="str">
         <v>AM FAIRMOUNT</v>
@@ -970,7 +983,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" xml:space="preserve">
       <c r="A16" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -998,8 +1011,9 @@
       <c r="I16" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J16" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J16" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K16" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1008,7 +1022,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" xml:space="preserve">
       <c r="A17" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1036,8 +1050,9 @@
       <c r="I17" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J17" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K17" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1046,7 +1061,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" xml:space="preserve">
       <c r="A18" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1074,8 +1089,9 @@
       <c r="I18" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J18" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J18" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K18" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1084,7 +1100,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" xml:space="preserve">
       <c r="A19" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1112,8 +1128,9 @@
       <c r="I19" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J19" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J19" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K19" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1122,7 +1139,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" xml:space="preserve">
       <c r="A20" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1150,8 +1167,9 @@
       <c r="I20" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J20" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J20" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K20" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1160,7 +1178,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" xml:space="preserve">
       <c r="A21" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1188,8 +1206,9 @@
       <c r="I21" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J21" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K21" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1198,7 +1217,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" xml:space="preserve">
       <c r="A22" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1226,8 +1245,9 @@
       <c r="I22" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J22" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J22" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K22" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1236,7 +1256,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" xml:space="preserve">
       <c r="A23" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1264,8 +1284,9 @@
       <c r="I23" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J23" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J23" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K23" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1274,7 +1295,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" xml:space="preserve">
       <c r="A24" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1302,8 +1323,9 @@
       <c r="I24" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J24" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K24" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1312,7 +1334,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" xml:space="preserve">
       <c r="A25" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE </v>
       </c>
@@ -1340,8 +1362,9 @@
       <c r="I25" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J25" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J25" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K25" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1350,7 +1373,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1378,8 +1401,9 @@
       <c r="I26" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J26" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K26" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1388,7 +1412,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" xml:space="preserve">
       <c r="A27" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1416,8 +1440,9 @@
       <c r="I27" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J27" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J27" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K27" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1426,7 +1451,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" xml:space="preserve">
       <c r="A28" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1454,8 +1479,9 @@
       <c r="I28" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J28" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J28" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K28" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1464,7 +1490,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" xml:space="preserve">
       <c r="A29" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1492,8 +1518,9 @@
       <c r="I29" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J29" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J29" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K29" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1502,7 +1529,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" xml:space="preserve">
       <c r="A30" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1530,8 +1557,9 @@
       <c r="I30" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J30" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J30" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K30" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1540,7 +1568,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1568,8 +1596,9 @@
       <c r="I31" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J31" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K31" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1578,7 +1607,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" xml:space="preserve">
       <c r="A32" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1606,8 +1635,9 @@
       <c r="I32" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J32" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J32" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K32" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1616,7 +1646,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" xml:space="preserve">
       <c r="A33" t="str">
         <v xml:space="preserve">#3: LEASING CENTER - INTERIOR SIGNAGE  </v>
       </c>
@@ -1644,8 +1674,9 @@
       <c r="I33" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J33" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K33" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1654,7 +1685,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" xml:space="preserve">
       <c r="A34" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1682,8 +1713,9 @@
       <c r="I34" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J34" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K34" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1692,7 +1724,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" xml:space="preserve">
       <c r="A35" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1720,8 +1752,9 @@
       <c r="I35" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J35" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J35" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K35" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1730,7 +1763,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" xml:space="preserve">
       <c r="A36" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1758,8 +1791,9 @@
       <c r="I36" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J36" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K36" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1768,7 +1802,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1796,8 +1830,9 @@
       <c r="I37" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J37" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K37" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1806,7 +1841,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" xml:space="preserve">
       <c r="A38" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1834,8 +1869,9 @@
       <c r="I38" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J38" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K38" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1844,7 +1880,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" xml:space="preserve">
       <c r="A39" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1872,8 +1908,9 @@
       <c r="I39" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J39" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J39" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K39" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1882,7 +1919,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" xml:space="preserve">
       <c r="A40" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1910,8 +1947,9 @@
       <c r="I40" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J40" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K40" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1920,7 +1958,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" xml:space="preserve">
       <c r="A41" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1948,8 +1986,9 @@
       <c r="I41" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J41" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J41" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K41" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1958,7 +1997,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" xml:space="preserve">
       <c r="A42" t="str">
         <v xml:space="preserve">#4: PARKING GARAGE - LEVEL B1 SIGNAGE </v>
       </c>
@@ -1986,8 +2025,9 @@
       <c r="I42" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J42" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J42" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K42" t="str">
         <v>AM FAIRMOUNT</v>
@@ -1996,7 +2036,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" xml:space="preserve">
       <c r="A43" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2024,8 +2064,9 @@
       <c r="I43" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J43" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K43" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2034,7 +2075,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" xml:space="preserve">
       <c r="A44" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2062,8 +2103,9 @@
       <c r="I44" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J44" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J44" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K44" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2072,7 +2114,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" xml:space="preserve">
       <c r="A45" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2100,8 +2142,9 @@
       <c r="I45" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J45" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K45" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2110,7 +2153,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" xml:space="preserve">
       <c r="A46" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2138,8 +2181,9 @@
       <c r="I46" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J46" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K46" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2148,7 +2192,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2176,8 +2220,9 @@
       <c r="I47" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J47" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K47" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2186,7 +2231,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" xml:space="preserve">
       <c r="A48" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2214,8 +2259,9 @@
       <c r="I48" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J48" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K48" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2224,7 +2270,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" xml:space="preserve">
       <c r="A49" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2252,8 +2298,9 @@
       <c r="I49" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J49" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K49" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2262,7 +2309,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" xml:space="preserve">
       <c r="A50" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2290,8 +2337,9 @@
       <c r="I50" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J50" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K50" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2300,7 +2348,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" xml:space="preserve">
       <c r="A51" t="str">
         <v xml:space="preserve">#5: PARKING GARAGE - LEVEL 1 SIGNAGE </v>
       </c>
@@ -2328,8 +2376,9 @@
       <c r="I51" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J51" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K51" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2338,7 +2387,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" xml:space="preserve">
       <c r="A52" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2366,8 +2415,9 @@
       <c r="I52" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J52" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K52" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2376,7 +2426,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" xml:space="preserve">
       <c r="A53" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2404,8 +2454,9 @@
       <c r="I53" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J53" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K53" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2414,7 +2465,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2442,8 +2493,9 @@
       <c r="I54" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J54" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K54" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2452,7 +2504,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" xml:space="preserve">
       <c r="A55" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2480,8 +2532,9 @@
       <c r="I55" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J55" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K55" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2490,7 +2543,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" xml:space="preserve">
       <c r="A56" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2518,8 +2571,9 @@
       <c r="I56" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J56" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K56" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2528,7 +2582,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" xml:space="preserve">
       <c r="A57" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2556,8 +2610,9 @@
       <c r="I57" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J57" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J57" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K57" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2566,7 +2621,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" xml:space="preserve">
       <c r="A58" t="str">
         <v xml:space="preserve">#6: PARKING GARAGE - LEVEL 2 SIGNAGE </v>
       </c>
@@ -2594,8 +2649,9 @@
       <c r="I58" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J58" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K58" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2604,7 +2660,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" xml:space="preserve">
       <c r="A59" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2632,8 +2688,9 @@
       <c r="I59" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J59" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K59" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2642,7 +2699,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" xml:space="preserve">
       <c r="A60" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2670,8 +2727,9 @@
       <c r="I60" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J60" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K60" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2680,7 +2738,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" xml:space="preserve">
       <c r="A61" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2708,8 +2766,9 @@
       <c r="I61" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J61" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K61" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2718,7 +2777,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" xml:space="preserve">
       <c r="A62" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2746,8 +2805,9 @@
       <c r="I62" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J62" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K62" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2756,7 +2816,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2784,8 +2844,9 @@
       <c r="I63" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J63" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K63" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2794,7 +2855,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" xml:space="preserve">
       <c r="A64" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2822,8 +2883,9 @@
       <c r="I64" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J64" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K64" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2832,7 +2894,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" xml:space="preserve">
       <c r="A65" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2860,8 +2922,9 @@
       <c r="I65" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J65" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K65" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2870,7 +2933,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" xml:space="preserve">
       <c r="A66" t="str">
         <v xml:space="preserve">#7: PARKING GARAGE - LEVEL 3 SIGNAGE </v>
       </c>
@@ -2898,8 +2961,9 @@
       <c r="I66" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J66" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K66" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2908,7 +2972,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" xml:space="preserve">
       <c r="A67" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -2936,8 +3000,9 @@
       <c r="I67" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J67" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K67" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2946,7 +3011,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" xml:space="preserve">
       <c r="A68" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -2974,8 +3039,9 @@
       <c r="I68" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J68" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K68" t="str">
         <v>AM FAIRMOUNT</v>
@@ -2984,7 +3050,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" xml:space="preserve">
       <c r="A69" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -3012,8 +3078,9 @@
       <c r="I69" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J69" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K69" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3022,7 +3089,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" xml:space="preserve">
       <c r="A70" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -3050,8 +3117,9 @@
       <c r="I70" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J70" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K70" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3060,7 +3128,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" xml:space="preserve">
       <c r="A71" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -3088,8 +3156,9 @@
       <c r="I71" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J71" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K71" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3098,7 +3167,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" xml:space="preserve">
       <c r="A72" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -3126,8 +3195,9 @@
       <c r="I72" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J72" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K72" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3136,7 +3206,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" xml:space="preserve">
       <c r="A73" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -3164,8 +3234,9 @@
       <c r="I73" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J73" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K73" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3174,7 +3245,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" xml:space="preserve">
       <c r="A74" t="str">
         <v xml:space="preserve">#8: PARKING GARAGE - LEVEL 4 SIGNAGE </v>
       </c>
@@ -3202,8 +3273,9 @@
       <c r="I74" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J74" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K74" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3212,7 +3284,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" xml:space="preserve">
       <c r="A75" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3240,8 +3312,9 @@
       <c r="I75" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J75" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J75" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K75" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3250,7 +3323,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" xml:space="preserve">
       <c r="A76" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3278,8 +3351,9 @@
       <c r="I76" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J76" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J76" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K76" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3288,7 +3362,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" xml:space="preserve">
       <c r="A77" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3316,8 +3390,9 @@
       <c r="I77" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J77" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K77" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3326,7 +3401,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" xml:space="preserve">
       <c r="A78" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3354,8 +3429,9 @@
       <c r="I78" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J78" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K78" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3364,7 +3440,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" xml:space="preserve">
       <c r="A79" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3392,8 +3468,9 @@
       <c r="I79" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J79" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K79" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3402,7 +3479,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" xml:space="preserve">
       <c r="A80" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3430,8 +3507,9 @@
       <c r="I80" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J80" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K80" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3440,7 +3518,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" xml:space="preserve">
       <c r="A81" t="str">
         <v xml:space="preserve">#9: PARKING GARAGE - LEVEL 5 SIGNAGE </v>
       </c>
@@ -3468,8 +3546,9 @@
       <c r="I81" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J81" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K81" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3478,7 +3557,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" xml:space="preserve">
       <c r="A82" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3506,8 +3585,9 @@
       <c r="I82" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J82" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K82" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3516,7 +3596,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" xml:space="preserve">
       <c r="A83" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3544,8 +3624,9 @@
       <c r="I83" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J83" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K83" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3554,7 +3635,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" xml:space="preserve">
       <c r="A84" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3582,8 +3663,9 @@
       <c r="I84" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J84" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K84" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3592,7 +3674,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" xml:space="preserve">
       <c r="A85" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3620,8 +3702,9 @@
       <c r="I85" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J85" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K85" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3630,7 +3713,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" xml:space="preserve">
       <c r="A86" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3658,8 +3741,9 @@
       <c r="I86" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J86" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K86" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3668,7 +3752,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" xml:space="preserve">
       <c r="A87" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3696,8 +3780,9 @@
       <c r="I87" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J87" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K87" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3706,7 +3791,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" xml:space="preserve">
       <c r="A88" t="str">
         <v xml:space="preserve">#10: PARKING GARAGE - LEVEL 6 SIGNAGE </v>
       </c>
@@ -3734,8 +3819,9 @@
       <c r="I88" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J88" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J88" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K88" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3744,7 +3830,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" xml:space="preserve">
       <c r="A89" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE </v>
       </c>
@@ -3772,8 +3858,9 @@
       <c r="I89" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J89" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K89" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3782,7 +3869,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" xml:space="preserve">
       <c r="A90" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE </v>
       </c>
@@ -3810,8 +3897,9 @@
       <c r="I90" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J90" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K90" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3820,7 +3908,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE  </v>
       </c>
@@ -3848,8 +3936,9 @@
       <c r="I91" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J91" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K91" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3858,7 +3947,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" xml:space="preserve">
       <c r="A92" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE  </v>
       </c>
@@ -3886,8 +3975,9 @@
       <c r="I92" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J92" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J92" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K92" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3896,7 +3986,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" xml:space="preserve">
       <c r="A93" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE  </v>
       </c>
@@ -3924,8 +4014,9 @@
       <c r="I93" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J93" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J93" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K93" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3934,7 +4025,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE  </v>
       </c>
@@ -3962,8 +4053,9 @@
       <c r="I94" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J94" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K94" t="str">
         <v>AM FAIRMOUNT</v>
@@ -3972,7 +4064,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" xml:space="preserve">
       <c r="A95" t="str">
         <v xml:space="preserve">#11: PARKING GARAGE - LEVEL 7 SIGNAGE  </v>
       </c>
@@ -4000,8 +4092,9 @@
       <c r="I95" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J95" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K95" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4010,7 +4103,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4038,8 +4131,9 @@
       <c r="I96" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J96" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K96" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4048,7 +4142,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" xml:space="preserve">
       <c r="A97" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4076,8 +4170,9 @@
       <c r="I97" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J97" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J97" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K97" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4086,7 +4181,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" xml:space="preserve">
       <c r="A98" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4114,8 +4209,9 @@
       <c r="I98" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J98" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J98" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K98" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4124,7 +4220,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" xml:space="preserve">
       <c r="A99" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4152,8 +4248,9 @@
       <c r="I99" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J99" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J99" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K99" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4162,7 +4259,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" xml:space="preserve">
       <c r="A100" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4190,8 +4287,9 @@
       <c r="I100" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J100" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J100" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K100" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4200,7 +4298,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" xml:space="preserve">
       <c r="A101" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4228,8 +4326,9 @@
       <c r="I101" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J101" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J101" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K101" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4238,7 +4337,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" xml:space="preserve">
       <c r="A102" t="str">
         <v xml:space="preserve">#12: PARKING GARAGE - LEVEL 8 SIGNAGE </v>
       </c>
@@ -4266,8 +4365,9 @@
       <c r="I102" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J102" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J102" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K102" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4276,7 +4376,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" xml:space="preserve">
       <c r="A103" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4304,8 +4404,9 @@
       <c r="I103" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J103" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J103" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K103" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4314,7 +4415,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" xml:space="preserve">
       <c r="A104" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4342,8 +4443,9 @@
       <c r="I104" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J104" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J104" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K104" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4352,7 +4454,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" xml:space="preserve">
       <c r="A105" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4380,8 +4482,9 @@
       <c r="I105" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J105" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J105" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K105" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4390,7 +4493,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" xml:space="preserve">
       <c r="A106" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4418,8 +4521,9 @@
       <c r="I106" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J106" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J106" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K106" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4428,7 +4532,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" xml:space="preserve">
       <c r="A107" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4456,8 +4560,9 @@
       <c r="I107" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J107" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J107" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K107" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4466,7 +4571,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" xml:space="preserve">
       <c r="A108" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4494,8 +4599,9 @@
       <c r="I108" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J108" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J108" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K108" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4504,7 +4610,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" xml:space="preserve">
       <c r="A109" t="str">
         <v xml:space="preserve">#13: PARKING GARAGE - LEVEL 9 SIGNAGE </v>
       </c>
@@ -4532,8 +4638,9 @@
       <c r="I109" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J109" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J109" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K109" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4542,7 +4649,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" xml:space="preserve">
       <c r="A110" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4570,8 +4677,9 @@
       <c r="I110" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J110" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J110" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K110" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4580,7 +4688,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" xml:space="preserve">
       <c r="A111" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4608,8 +4716,9 @@
       <c r="I111" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J111" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J111" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K111" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4618,7 +4727,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" xml:space="preserve">
       <c r="A112" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4646,8 +4755,9 @@
       <c r="I112" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J112" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J112" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K112" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4656,7 +4766,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" xml:space="preserve">
       <c r="A113" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4684,8 +4794,9 @@
       <c r="I113" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J113" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J113" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K113" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4694,7 +4805,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" xml:space="preserve">
       <c r="A114" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4722,8 +4833,9 @@
       <c r="I114" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J114" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J114" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K114" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4732,7 +4844,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" xml:space="preserve">
       <c r="A115" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4760,8 +4872,9 @@
       <c r="I115" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J115" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J115" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K115" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4770,7 +4883,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" xml:space="preserve">
       <c r="A116" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4798,8 +4911,9 @@
       <c r="I116" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J116" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J116" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K116" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4808,7 +4922,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" xml:space="preserve">
       <c r="A117" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4836,8 +4950,9 @@
       <c r="I117" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J117" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J117" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K117" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4846,7 +4961,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" xml:space="preserve">
       <c r="A118" t="str">
         <v xml:space="preserve">#14: LEVEL 1 SIGNAGE </v>
       </c>
@@ -4874,8 +4989,9 @@
       <c r="I118" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J118" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J118" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K118" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4884,7 +5000,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" xml:space="preserve">
       <c r="A119" t="str">
         <v xml:space="preserve">#15: LEVEL 2 SIGNAGE </v>
       </c>
@@ -4912,8 +5028,9 @@
       <c r="I119" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J119" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J119" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K119" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4922,7 +5039,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" xml:space="preserve">
       <c r="A120" t="str">
         <v xml:space="preserve">#15: LEVEL 2 SIGNAGE </v>
       </c>
@@ -4950,8 +5067,9 @@
       <c r="I120" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J120" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J120" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K120" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4960,7 +5078,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" xml:space="preserve">
       <c r="A121" t="str">
         <v xml:space="preserve">#15: LEVEL 2 SIGNAGE </v>
       </c>
@@ -4988,8 +5106,9 @@
       <c r="I121" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J121" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J121" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K121" t="str">
         <v>AM FAIRMOUNT</v>
@@ -4998,7 +5117,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" xml:space="preserve">
       <c r="A122" t="str">
         <v xml:space="preserve">#15: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5026,8 +5145,9 @@
       <c r="I122" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J122" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J122" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K122" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5036,7 +5156,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" xml:space="preserve">
       <c r="A123" t="str">
         <v xml:space="preserve">#15: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5064,8 +5184,9 @@
       <c r="I123" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J123" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J123" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K123" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5074,7 +5195,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" xml:space="preserve">
       <c r="A124" t="str">
         <v xml:space="preserve">#15: LEVEL 2 SIGNAGE  </v>
       </c>
@@ -5102,8 +5223,9 @@
       <c r="I124" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J124" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J124" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K124" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5112,7 +5234,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" xml:space="preserve">
       <c r="A125" t="str">
         <v xml:space="preserve">#16: LEVEL 3 SIGNAGE </v>
       </c>
@@ -5140,8 +5262,9 @@
       <c r="I125" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J125" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J125" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K125" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5150,7 +5273,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" xml:space="preserve">
       <c r="A126" t="str">
         <v xml:space="preserve">#16: LEVEL 3 SIGNAGE </v>
       </c>
@@ -5178,8 +5301,9 @@
       <c r="I126" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J126" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J126" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K126" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5188,7 +5312,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" xml:space="preserve">
       <c r="A127" t="str">
         <v xml:space="preserve">#16: LEVEL 3 SIGNAGE </v>
       </c>
@@ -5216,8 +5340,9 @@
       <c r="I127" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J127" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J127" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K127" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5226,7 +5351,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" xml:space="preserve">
       <c r="A128" t="str">
         <v xml:space="preserve">#17: LEVEL 4 SIGNAGE </v>
       </c>
@@ -5254,8 +5379,9 @@
       <c r="I128" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J128" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J128" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K128" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5264,7 +5390,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" xml:space="preserve">
       <c r="A129" t="str">
         <v xml:space="preserve">#17: LEVEL 4 SIGNAGE </v>
       </c>
@@ -5292,8 +5418,9 @@
       <c r="I129" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J129" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J129" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K129" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5302,7 +5429,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" xml:space="preserve">
       <c r="A130" t="str">
         <v xml:space="preserve">#17: LEVEL 4 SIGNAGE </v>
       </c>
@@ -5330,8 +5457,9 @@
       <c r="I130" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J130" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J130" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K130" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5340,7 +5468,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" xml:space="preserve">
       <c r="A131" t="str">
         <v xml:space="preserve">#18: LEVEL 5 SIGNAGE </v>
       </c>
@@ -5368,8 +5496,9 @@
       <c r="I131" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J131" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J131" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K131" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5378,7 +5507,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" xml:space="preserve">
       <c r="A132" t="str">
         <v xml:space="preserve">#18: LEVEL 5 SIGNAGE </v>
       </c>
@@ -5406,8 +5535,9 @@
       <c r="I132" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J132" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J132" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K132" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5416,7 +5546,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" xml:space="preserve">
       <c r="A133" t="str">
         <v xml:space="preserve">#18: LEVEL 5 SIGNAGE </v>
       </c>
@@ -5444,8 +5574,9 @@
       <c r="I133" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J133" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J133" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K133" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5454,7 +5585,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" xml:space="preserve">
       <c r="A134" t="str">
         <v xml:space="preserve">#19: LEVEL 6 SIGNAGE </v>
       </c>
@@ -5482,8 +5613,9 @@
       <c r="I134" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J134" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J134" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K134" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5492,7 +5624,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" xml:space="preserve">
       <c r="A135" t="str">
         <v xml:space="preserve">#19: LEVEL 6 SIGNAGE </v>
       </c>
@@ -5520,8 +5652,9 @@
       <c r="I135" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J135" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J135" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K135" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5530,7 +5663,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" xml:space="preserve">
       <c r="A136" t="str">
         <v xml:space="preserve">#19: LEVEL 6 SIGNAGE </v>
       </c>
@@ -5558,8 +5691,9 @@
       <c r="I136" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J136" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J136" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K136" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5568,7 +5702,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" xml:space="preserve">
       <c r="A137" t="str">
         <v xml:space="preserve">#20: LEVEL 7 SIGNAGE </v>
       </c>
@@ -5596,8 +5730,9 @@
       <c r="I137" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J137" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J137" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K137" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5606,7 +5741,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" xml:space="preserve">
       <c r="A138" t="str">
         <v xml:space="preserve">#20: LEVEL 7 SIGNAGE </v>
       </c>
@@ -5634,8 +5769,9 @@
       <c r="I138" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J138" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J138" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K138" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5644,7 +5780,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" xml:space="preserve">
       <c r="A139" t="str">
         <v xml:space="preserve">#20: LEVEL 7 SIGNAGE </v>
       </c>
@@ -5672,8 +5808,9 @@
       <c r="I139" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J139" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J139" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K139" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5682,7 +5819,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" xml:space="preserve">
       <c r="A140" t="str">
         <v xml:space="preserve">#21: LEVEL 8 SIGNAGE </v>
       </c>
@@ -5710,8 +5847,9 @@
       <c r="I140" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J140" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J140" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K140" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5720,7 +5858,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" xml:space="preserve">
       <c r="A141" t="str">
         <v xml:space="preserve">#21: LEVEL 8 SIGNAGE </v>
       </c>
@@ -5748,8 +5886,9 @@
       <c r="I141" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J141" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J141" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K141" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5758,7 +5897,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" xml:space="preserve">
       <c r="A142" t="str">
         <v xml:space="preserve">#21: LEVEL 8 SIGNAGE </v>
       </c>
@@ -5786,8 +5925,9 @@
       <c r="I142" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J142" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J142" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K142" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5796,7 +5936,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" xml:space="preserve">
       <c r="A143" t="str">
         <v xml:space="preserve">#22: LEVEL 9 SIGNAGE </v>
       </c>
@@ -5824,8 +5964,9 @@
       <c r="I143" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J143" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J143" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K143" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5834,7 +5975,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" xml:space="preserve">
       <c r="A144" t="str">
         <v xml:space="preserve">#22: LEVEL 9 SIGNAGE </v>
       </c>
@@ -5862,8 +6003,9 @@
       <c r="I144" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J144" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J144" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K144" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5872,7 +6014,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" xml:space="preserve">
       <c r="A145" t="str">
         <v xml:space="preserve">#22: LEVEL 9 SIGNAGE </v>
       </c>
@@ -5900,8 +6042,9 @@
       <c r="I145" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J145" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J145" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K145" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5910,7 +6053,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" xml:space="preserve">
       <c r="A146" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -5938,8 +6081,9 @@
       <c r="I146" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J146" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J146" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K146" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5948,7 +6092,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" xml:space="preserve">
       <c r="A147" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -5976,8 +6120,9 @@
       <c r="I147" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J147" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J147" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K147" t="str">
         <v>AM FAIRMOUNT</v>
@@ -5986,7 +6131,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" xml:space="preserve">
       <c r="A148" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6014,8 +6159,9 @@
       <c r="I148" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J148" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J148" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K148" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6024,7 +6170,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" xml:space="preserve">
       <c r="A149" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6052,8 +6198,9 @@
       <c r="I149" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J149" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J149" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K149" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6062,7 +6209,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" xml:space="preserve">
       <c r="A150" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6090,8 +6237,9 @@
       <c r="I150" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J150" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J150" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K150" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6100,7 +6248,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" xml:space="preserve">
       <c r="A151" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6128,8 +6276,9 @@
       <c r="I151" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J151" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J151" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K151" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6138,7 +6287,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" xml:space="preserve">
       <c r="A152" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6166,8 +6315,9 @@
       <c r="I152" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J152" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J152" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K152" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6176,7 +6326,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" xml:space="preserve">
       <c r="A153" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6204,8 +6354,9 @@
       <c r="I153" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J153" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J153" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K153" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6214,7 +6365,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" xml:space="preserve">
       <c r="A154" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6242,8 +6393,9 @@
       <c r="I154" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J154" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J154" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K154" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6252,7 +6404,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" xml:space="preserve">
       <c r="A155" t="str">
         <v xml:space="preserve">#23: LEVEL 10 SIGNAGE </v>
       </c>
@@ -6280,8 +6432,9 @@
       <c r="I155" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J155" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J155" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K155" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6290,7 +6443,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" xml:space="preserve">
       <c r="A156" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6318,8 +6471,9 @@
       <c r="I156" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J156" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J156" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K156" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6328,7 +6482,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" xml:space="preserve">
       <c r="A157" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6356,8 +6510,9 @@
       <c r="I157" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J157" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J157" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K157" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6366,7 +6521,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" xml:space="preserve">
       <c r="A158" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6394,8 +6549,9 @@
       <c r="I158" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J158" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J158" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K158" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6404,7 +6560,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" xml:space="preserve">
       <c r="A159" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6432,8 +6588,9 @@
       <c r="I159" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J159" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J159" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K159" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6442,7 +6599,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" xml:space="preserve">
       <c r="A160" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6470,8 +6627,9 @@
       <c r="I160" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J160" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J160" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K160" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6480,7 +6638,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" xml:space="preserve">
       <c r="A161" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6508,8 +6666,9 @@
       <c r="I161" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J161" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J161" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K161" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6518,7 +6677,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" xml:space="preserve">
       <c r="A162" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6546,8 +6705,9 @@
       <c r="I162" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J162" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J162" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K162" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6556,7 +6716,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" xml:space="preserve">
       <c r="A163" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6584,8 +6744,9 @@
       <c r="I163" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J163" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J163" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K163" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6594,7 +6755,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" xml:space="preserve">
       <c r="A164" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6622,8 +6783,9 @@
       <c r="I164" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J164" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J164" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K164" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6632,7 +6794,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" xml:space="preserve">
       <c r="A165" t="str">
         <v xml:space="preserve">#24: LEVEL 11 SIGNAGE </v>
       </c>
@@ -6660,8 +6822,9 @@
       <c r="I165" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J165" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J165" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K165" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6670,7 +6833,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" xml:space="preserve">
       <c r="A166" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6698,8 +6861,9 @@
       <c r="I166" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J166" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J166" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K166" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6708,7 +6872,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" xml:space="preserve">
       <c r="A167" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6736,8 +6900,9 @@
       <c r="I167" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J167" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J167" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K167" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6746,7 +6911,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" xml:space="preserve">
       <c r="A168" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6774,8 +6939,9 @@
       <c r="I168" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J168" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J168" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K168" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6784,7 +6950,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" xml:space="preserve">
       <c r="A169" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6812,8 +6978,9 @@
       <c r="I169" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J169" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J169" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K169" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6822,7 +6989,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" xml:space="preserve">
       <c r="A170" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6850,8 +7017,9 @@
       <c r="I170" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J170" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J170" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K170" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6860,7 +7028,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" xml:space="preserve">
       <c r="A171" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6888,8 +7056,9 @@
       <c r="I171" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J171" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J171" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K171" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6898,7 +7067,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" xml:space="preserve">
       <c r="A172" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6926,8 +7095,9 @@
       <c r="I172" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J172" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J172" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K172" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6936,7 +7106,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" xml:space="preserve">
       <c r="A173" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -6964,8 +7134,9 @@
       <c r="I173" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J173" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J173" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K173" t="str">
         <v>AM FAIRMOUNT</v>
@@ -6974,7 +7145,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" xml:space="preserve">
       <c r="A174" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -7002,8 +7173,9 @@
       <c r="I174" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J174" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J174" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K174" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7012,7 +7184,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" xml:space="preserve">
       <c r="A175" t="str">
         <v xml:space="preserve">#25: LEVEL 12 SIGNAGE </v>
       </c>
@@ -7040,8 +7212,9 @@
       <c r="I175" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J175" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J175" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K175" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7050,7 +7223,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" xml:space="preserve">
       <c r="A176" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7078,8 +7251,9 @@
       <c r="I176" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J176" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J176" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K176" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7088,7 +7262,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" xml:space="preserve">
       <c r="A177" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7116,8 +7290,9 @@
       <c r="I177" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J177" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J177" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K177" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7126,7 +7301,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" xml:space="preserve">
       <c r="A178" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7154,8 +7329,9 @@
       <c r="I178" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J178" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J178" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K178" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7164,7 +7340,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" xml:space="preserve">
       <c r="A179" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7192,8 +7368,9 @@
       <c r="I179" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J179" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J179" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K179" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7202,7 +7379,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" xml:space="preserve">
       <c r="A180" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7230,8 +7407,9 @@
       <c r="I180" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J180" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J180" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K180" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7240,7 +7418,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" xml:space="preserve">
       <c r="A181" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7268,8 +7446,9 @@
       <c r="I181" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J181" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J181" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K181" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7278,7 +7457,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" xml:space="preserve">
       <c r="A182" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7306,8 +7485,9 @@
       <c r="I182" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J182" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J182" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K182" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7316,7 +7496,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" xml:space="preserve">
       <c r="A183" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7344,8 +7524,9 @@
       <c r="I183" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J183" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J183" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K183" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7354,7 +7535,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" xml:space="preserve">
       <c r="A184" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7382,8 +7563,9 @@
       <c r="I184" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J184" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J184" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K184" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7392,7 +7574,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" xml:space="preserve">
       <c r="A185" t="str">
         <v xml:space="preserve">#26: LEVEL 14 SIGNAGE </v>
       </c>
@@ -7420,8 +7602,9 @@
       <c r="I185" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J185" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J185" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K185" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7430,7 +7613,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" xml:space="preserve">
       <c r="A186" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7458,8 +7641,9 @@
       <c r="I186" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J186" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J186" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K186" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7468,7 +7652,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" xml:space="preserve">
       <c r="A187" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7496,8 +7680,9 @@
       <c r="I187" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J187" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J187" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K187" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7506,7 +7691,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" xml:space="preserve">
       <c r="A188" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7534,8 +7719,9 @@
       <c r="I188" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J188" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J188" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K188" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7544,7 +7730,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" xml:space="preserve">
       <c r="A189" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7572,8 +7758,9 @@
       <c r="I189" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J189" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J189" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K189" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7582,7 +7769,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" xml:space="preserve">
       <c r="A190" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7610,8 +7797,9 @@
       <c r="I190" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J190" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J190" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K190" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7620,7 +7808,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" xml:space="preserve">
       <c r="A191" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7648,8 +7836,9 @@
       <c r="I191" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J191" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J191" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K191" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7658,7 +7847,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" xml:space="preserve">
       <c r="A192" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7686,8 +7875,9 @@
       <c r="I192" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J192" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J192" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K192" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7696,7 +7886,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" xml:space="preserve">
       <c r="A193" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7724,8 +7914,9 @@
       <c r="I193" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J193" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J193" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K193" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7734,7 +7925,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" xml:space="preserve">
       <c r="A194" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7762,8 +7953,9 @@
       <c r="I194" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J194" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J194" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K194" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7772,7 +7964,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" xml:space="preserve">
       <c r="A195" t="str">
         <v xml:space="preserve">#27: LEVEL 15 SIGNAGE </v>
       </c>
@@ -7800,8 +7992,9 @@
       <c r="I195" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J195" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J195" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K195" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7810,7 +8003,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" xml:space="preserve">
       <c r="A196" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -7838,8 +8031,9 @@
       <c r="I196" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J196" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J196" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K196" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7848,7 +8042,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" xml:space="preserve">
       <c r="A197" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -7876,8 +8070,9 @@
       <c r="I197" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J197" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J197" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K197" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7886,7 +8081,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" xml:space="preserve">
       <c r="A198" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -7914,8 +8109,9 @@
       <c r="I198" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J198" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J198" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K198" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7924,7 +8120,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" xml:space="preserve">
       <c r="A199" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -7952,8 +8148,9 @@
       <c r="I199" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J199" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J199" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K199" t="str">
         <v>AM FAIRMOUNT</v>
@@ -7962,7 +8159,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" xml:space="preserve">
       <c r="A200" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -7990,8 +8187,9 @@
       <c r="I200" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J200" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J200" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K200" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8000,7 +8198,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" xml:space="preserve">
       <c r="A201" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -8028,8 +8226,9 @@
       <c r="I201" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J201" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J201" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K201" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8038,7 +8237,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" xml:space="preserve">
       <c r="A202" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -8066,8 +8265,9 @@
       <c r="I202" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J202" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J202" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K202" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8076,7 +8276,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" xml:space="preserve">
       <c r="A203" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -8104,8 +8304,9 @@
       <c r="I203" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J203" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J203" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K203" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8114,7 +8315,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" xml:space="preserve">
       <c r="A204" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -8142,8 +8343,9 @@
       <c r="I204" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J204" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J204" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K204" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8152,7 +8354,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" xml:space="preserve">
       <c r="A205" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -8180,8 +8382,9 @@
       <c r="I205" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J205" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J205" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K205" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8190,7 +8393,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" xml:space="preserve">
       <c r="A206" t="str">
         <v xml:space="preserve">#28: LEVEL 16 SIGNAGE </v>
       </c>
@@ -8218,8 +8421,9 @@
       <c r="I206" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J206" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J206" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K206" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8228,7 +8432,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" xml:space="preserve">
       <c r="A207" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE </v>
       </c>
@@ -8256,8 +8460,9 @@
       <c r="I207" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J207" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J207" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K207" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8266,7 +8471,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" xml:space="preserve">
       <c r="A208" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE </v>
       </c>
@@ -8294,8 +8499,9 @@
       <c r="I208" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J208" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J208" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K208" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8304,7 +8510,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" xml:space="preserve">
       <c r="A209" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE </v>
       </c>
@@ -8332,8 +8538,9 @@
       <c r="I209" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J209" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J209" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K209" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8342,7 +8549,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" xml:space="preserve">
       <c r="A210" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8370,8 +8577,9 @@
       <c r="I210" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J210" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J210" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K210" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8380,7 +8588,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" xml:space="preserve">
       <c r="A211" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8408,8 +8616,9 @@
       <c r="I211" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J211" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J211" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K211" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8418,7 +8627,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" xml:space="preserve">
       <c r="A212" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8446,8 +8655,9 @@
       <c r="I212" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J212" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J212" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K212" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8456,7 +8666,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" xml:space="preserve">
       <c r="A213" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8484,8 +8694,9 @@
       <c r="I213" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J213" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J213" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K213" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8494,7 +8705,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" xml:space="preserve">
       <c r="A214" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8522,8 +8733,9 @@
       <c r="I214" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J214" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J214" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K214" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8532,7 +8744,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" xml:space="preserve">
       <c r="A215" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8560,8 +8772,9 @@
       <c r="I215" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J215" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J215" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K215" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8570,7 +8783,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" xml:space="preserve">
       <c r="A216" t="str">
         <v xml:space="preserve">#29: LEVEL 17 SIGNAGE  </v>
       </c>
@@ -8598,8 +8811,9 @@
       <c r="I216" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J216" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J216" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K216" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8608,7 +8822,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" xml:space="preserve">
       <c r="A217" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8636,8 +8850,9 @@
       <c r="I217" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J217" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J217" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K217" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8646,7 +8861,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" xml:space="preserve">
       <c r="A218" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8674,8 +8889,9 @@
       <c r="I218" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J218" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J218" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K218" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8684,7 +8900,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" xml:space="preserve">
       <c r="A219" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8712,8 +8928,9 @@
       <c r="I219" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J219" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J219" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K219" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8722,7 +8939,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" xml:space="preserve">
       <c r="A220" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8750,8 +8967,9 @@
       <c r="I220" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J220" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J220" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K220" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8760,7 +8978,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" xml:space="preserve">
       <c r="A221" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8788,8 +9006,9 @@
       <c r="I221" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J221" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J221" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K221" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8798,7 +9017,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" xml:space="preserve">
       <c r="A222" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8826,8 +9045,9 @@
       <c r="I222" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J222" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J222" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K222" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8836,7 +9056,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" xml:space="preserve">
       <c r="A223" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8864,8 +9084,9 @@
       <c r="I223" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J223" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J223" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K223" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8874,7 +9095,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" xml:space="preserve">
       <c r="A224" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8902,8 +9123,9 @@
       <c r="I224" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J224" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J224" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K224" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8912,7 +9134,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" xml:space="preserve">
       <c r="A225" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8940,8 +9162,9 @@
       <c r="I225" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J225" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J225" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K225" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8950,7 +9173,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" xml:space="preserve">
       <c r="A226" t="str">
         <v xml:space="preserve">#30: LEVEL 18 SIGNAGE </v>
       </c>
@@ -8978,8 +9201,9 @@
       <c r="I226" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J226" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J226" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K226" t="str">
         <v>AM FAIRMOUNT</v>
@@ -8988,7 +9212,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" xml:space="preserve">
       <c r="A227" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9016,8 +9240,9 @@
       <c r="I227" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J227" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J227" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K227" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9026,7 +9251,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" xml:space="preserve">
       <c r="A228" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9054,8 +9279,9 @@
       <c r="I228" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J228" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J228" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K228" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9064,7 +9290,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" xml:space="preserve">
       <c r="A229" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9092,8 +9318,9 @@
       <c r="I229" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J229" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J229" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K229" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9102,7 +9329,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" xml:space="preserve">
       <c r="A230" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9130,8 +9357,9 @@
       <c r="I230" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J230" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J230" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K230" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9140,7 +9368,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" xml:space="preserve">
       <c r="A231" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9168,8 +9396,9 @@
       <c r="I231" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J231" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J231" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K231" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9178,7 +9407,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" xml:space="preserve">
       <c r="A232" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9206,8 +9435,9 @@
       <c r="I232" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J232" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J232" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K232" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9216,7 +9446,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" xml:space="preserve">
       <c r="A233" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9244,8 +9474,9 @@
       <c r="I233" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J233" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J233" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K233" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9254,7 +9485,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" xml:space="preserve">
       <c r="A234" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9282,8 +9513,9 @@
       <c r="I234" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J234" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J234" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K234" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9292,7 +9524,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" xml:space="preserve">
       <c r="A235" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9320,8 +9552,9 @@
       <c r="I235" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J235" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J235" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K235" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9330,7 +9563,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" xml:space="preserve">
       <c r="A236" t="str">
         <v xml:space="preserve">#31: LEVEL 19 SIGNAGE </v>
       </c>
@@ -9358,8 +9591,9 @@
       <c r="I236" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J236" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J236" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K236" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9368,7 +9602,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" xml:space="preserve">
       <c r="A237" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE </v>
       </c>
@@ -9396,8 +9630,9 @@
       <c r="I237" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J237" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J237" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K237" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9406,7 +9641,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" xml:space="preserve">
       <c r="A238" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE </v>
       </c>
@@ -9434,8 +9669,9 @@
       <c r="I238" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J238" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J238" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K238" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9444,7 +9680,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" xml:space="preserve">
       <c r="A239" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE </v>
       </c>
@@ -9472,8 +9708,9 @@
       <c r="I239" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J239" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J239" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K239" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9482,7 +9719,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" xml:space="preserve">
       <c r="A240" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE </v>
       </c>
@@ -9510,8 +9747,9 @@
       <c r="I240" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J240" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J240" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K240" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9520,7 +9758,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" xml:space="preserve">
       <c r="A241" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE </v>
       </c>
@@ -9548,8 +9786,9 @@
       <c r="I241" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J241" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J241" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K241" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9558,7 +9797,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" xml:space="preserve">
       <c r="A242" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE  </v>
       </c>
@@ -9586,8 +9825,9 @@
       <c r="I242" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J242" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J242" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K242" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9596,7 +9836,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" xml:space="preserve">
       <c r="A243" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE  </v>
       </c>
@@ -9624,8 +9864,9 @@
       <c r="I243" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J243" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J243" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K243" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9634,7 +9875,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" xml:space="preserve">
       <c r="A244" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE  </v>
       </c>
@@ -9662,8 +9903,9 @@
       <c r="I244" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J244" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J244" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K244" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9672,7 +9914,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" xml:space="preserve">
       <c r="A245" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE  </v>
       </c>
@@ -9700,8 +9942,9 @@
       <c r="I245" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J245" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J245" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K245" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9710,7 +9953,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" xml:space="preserve">
       <c r="A246" t="str">
         <v xml:space="preserve">#32: LEVEL 20 SIGNAGE  </v>
       </c>
@@ -9738,8 +9981,9 @@
       <c r="I246" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J246" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J246" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K246" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9748,7 +9992,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" xml:space="preserve">
       <c r="A247" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -9776,8 +10020,9 @@
       <c r="I247" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J247" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J247" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K247" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9786,7 +10031,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" xml:space="preserve">
       <c r="A248" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -9814,8 +10059,9 @@
       <c r="I248" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J248" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J248" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K248" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9824,7 +10070,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" xml:space="preserve">
       <c r="A249" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -9852,8 +10098,9 @@
       <c r="I249" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J249" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J249" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K249" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9862,7 +10109,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" xml:space="preserve">
       <c r="A250" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -9890,8 +10137,9 @@
       <c r="I250" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J250" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J250" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K250" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9900,7 +10148,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" xml:space="preserve">
       <c r="A251" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -9928,8 +10176,9 @@
       <c r="I251" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J251" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J251" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K251" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9938,7 +10187,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" xml:space="preserve">
       <c r="A252" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -9966,8 +10215,9 @@
       <c r="I252" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J252" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J252" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K252" t="str">
         <v>AM FAIRMOUNT</v>
@@ -9976,7 +10226,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" xml:space="preserve">
       <c r="A253" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -10004,8 +10254,9 @@
       <c r="I253" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J253" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J253" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K253" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10014,7 +10265,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" xml:space="preserve">
       <c r="A254" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -10042,8 +10293,9 @@
       <c r="I254" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J254" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J254" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K254" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10052,7 +10304,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" xml:space="preserve">
       <c r="A255" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -10080,8 +10332,9 @@
       <c r="I255" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J255" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J255" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K255" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10090,7 +10343,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" xml:space="preserve">
       <c r="A256" t="str">
         <v xml:space="preserve">#33: LEVEL 21 SIGNAGE </v>
       </c>
@@ -10118,8 +10371,9 @@
       <c r="I256" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J256" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J256" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K256" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10128,7 +10382,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" xml:space="preserve">
       <c r="A257" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10156,8 +10410,9 @@
       <c r="I257" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J257" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J257" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K257" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10166,7 +10421,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" xml:space="preserve">
       <c r="A258" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10194,8 +10449,9 @@
       <c r="I258" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J258" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J258" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K258" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10204,7 +10460,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" xml:space="preserve">
       <c r="A259" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10232,8 +10488,9 @@
       <c r="I259" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J259" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J259" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K259" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10242,7 +10499,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" xml:space="preserve">
       <c r="A260" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10270,8 +10527,9 @@
       <c r="I260" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J260" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J260" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K260" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10280,7 +10538,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" xml:space="preserve">
       <c r="A261" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10308,8 +10566,9 @@
       <c r="I261" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J261" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J261" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K261" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10318,7 +10577,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" xml:space="preserve">
       <c r="A262" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10346,8 +10605,9 @@
       <c r="I262" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J262" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J262" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K262" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10356,7 +10616,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" xml:space="preserve">
       <c r="A263" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10384,8 +10644,9 @@
       <c r="I263" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J263" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J263" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K263" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10394,7 +10655,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" xml:space="preserve">
       <c r="A264" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10422,8 +10683,9 @@
       <c r="I264" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J264" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J264" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K264" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10432,7 +10694,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" xml:space="preserve">
       <c r="A265" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10460,8 +10722,9 @@
       <c r="I265" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J265" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J265" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K265" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10470,7 +10733,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" xml:space="preserve">
       <c r="A266" t="str">
         <v xml:space="preserve">#34: LEVEL 22 SIGNAGE </v>
       </c>
@@ -10498,8 +10761,9 @@
       <c r="I266" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J266" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J266" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K266" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10508,7 +10772,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" xml:space="preserve">
       <c r="A267" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10536,8 +10800,9 @@
       <c r="I267" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J267" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J267" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K267" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10546,7 +10811,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" xml:space="preserve">
       <c r="A268" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10574,8 +10839,9 @@
       <c r="I268" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J268" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J268" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K268" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10584,7 +10850,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" xml:space="preserve">
       <c r="A269" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10612,8 +10878,9 @@
       <c r="I269" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J269" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J269" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K269" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10622,7 +10889,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" xml:space="preserve">
       <c r="A270" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10650,8 +10917,9 @@
       <c r="I270" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J270" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J270" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K270" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10660,7 +10928,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" xml:space="preserve">
       <c r="A271" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10688,8 +10956,9 @@
       <c r="I271" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J271" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J271" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K271" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10698,7 +10967,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" xml:space="preserve">
       <c r="A272" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10726,8 +10995,9 @@
       <c r="I272" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J272" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J272" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K272" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10736,7 +11006,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" xml:space="preserve">
       <c r="A273" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10764,8 +11034,9 @@
       <c r="I273" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J273" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J273" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K273" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10774,7 +11045,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" xml:space="preserve">
       <c r="A274" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10802,8 +11073,9 @@
       <c r="I274" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J274" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J274" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K274" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10812,7 +11084,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" xml:space="preserve">
       <c r="A275" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10840,8 +11112,9 @@
       <c r="I275" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J275" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J275" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K275" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10850,7 +11123,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" xml:space="preserve">
       <c r="A276" t="str">
         <v xml:space="preserve">#35: LEVEL 23 SIGNAGE </v>
       </c>
@@ -10878,8 +11151,9 @@
       <c r="I276" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J276" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J276" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K276" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10888,7 +11162,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" xml:space="preserve">
       <c r="A277" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -10916,8 +11190,9 @@
       <c r="I277" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J277" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J277" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K277" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10926,7 +11201,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" xml:space="preserve">
       <c r="A278" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -10954,8 +11229,9 @@
       <c r="I278" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J278" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J278" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K278" t="str">
         <v>AM FAIRMOUNT</v>
@@ -10964,7 +11240,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" xml:space="preserve">
       <c r="A279" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -10992,8 +11268,9 @@
       <c r="I279" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J279" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J279" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K279" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11002,7 +11279,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" xml:space="preserve">
       <c r="A280" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11030,8 +11307,9 @@
       <c r="I280" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J280" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J280" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K280" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11040,7 +11318,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" xml:space="preserve">
       <c r="A281" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11068,8 +11346,9 @@
       <c r="I281" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J281" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J281" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K281" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11078,7 +11357,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" xml:space="preserve">
       <c r="A282" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11106,8 +11385,9 @@
       <c r="I282" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J282" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J282" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K282" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11116,7 +11396,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" xml:space="preserve">
       <c r="A283" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11144,8 +11424,9 @@
       <c r="I283" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J283" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J283" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K283" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11154,7 +11435,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" xml:space="preserve">
       <c r="A284" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11182,8 +11463,9 @@
       <c r="I284" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J284" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J284" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K284" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11192,7 +11474,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" xml:space="preserve">
       <c r="A285" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11220,8 +11502,9 @@
       <c r="I285" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J285" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J285" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K285" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11230,7 +11513,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" xml:space="preserve">
       <c r="A286" t="str">
         <v xml:space="preserve">#36: LEVEL 24 SIGNAGE </v>
       </c>
@@ -11258,8 +11541,9 @@
       <c r="I286" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J286" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J286" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K286" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11268,7 +11552,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" xml:space="preserve">
       <c r="A287" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11296,8 +11580,9 @@
       <c r="I287" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J287" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J287" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K287" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11306,7 +11591,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" xml:space="preserve">
       <c r="A288" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11334,8 +11619,9 @@
       <c r="I288" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J288" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J288" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K288" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11344,7 +11630,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" xml:space="preserve">
       <c r="A289" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11372,8 +11658,9 @@
       <c r="I289" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J289" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J289" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K289" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11382,7 +11669,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" xml:space="preserve">
       <c r="A290" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11410,8 +11697,9 @@
       <c r="I290" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J290" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J290" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K290" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11420,7 +11708,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" xml:space="preserve">
       <c r="A291" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11448,8 +11736,9 @@
       <c r="I291" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J291" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J291" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K291" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11458,7 +11747,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" xml:space="preserve">
       <c r="A292" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11486,8 +11775,9 @@
       <c r="I292" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J292" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J292" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K292" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11496,7 +11786,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" xml:space="preserve">
       <c r="A293" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11524,8 +11814,9 @@
       <c r="I293" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J293" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J293" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K293" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11534,7 +11825,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" xml:space="preserve">
       <c r="A294" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11562,8 +11853,9 @@
       <c r="I294" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J294" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J294" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K294" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11572,7 +11864,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" xml:space="preserve">
       <c r="A295" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11600,8 +11892,9 @@
       <c r="I295" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J295" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J295" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K295" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11610,7 +11903,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" xml:space="preserve">
       <c r="A296" t="str">
         <v xml:space="preserve">#37: LEVEL 25 SIGNAGE </v>
       </c>
@@ -11638,8 +11931,9 @@
       <c r="I296" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J296" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J296" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K296" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11648,7 +11942,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" xml:space="preserve">
       <c r="A297" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11676,8 +11970,9 @@
       <c r="I297" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J297" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J297" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K297" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11686,7 +11981,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" xml:space="preserve">
       <c r="A298" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11714,8 +12009,9 @@
       <c r="I298" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J298" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J298" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K298" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11724,7 +12020,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" xml:space="preserve">
       <c r="A299" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11752,8 +12048,9 @@
       <c r="I299" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J299" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J299" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K299" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11762,7 +12059,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" xml:space="preserve">
       <c r="A300" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11790,8 +12087,9 @@
       <c r="I300" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J300" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J300" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K300" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11800,7 +12098,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" xml:space="preserve">
       <c r="A301" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11828,8 +12126,9 @@
       <c r="I301" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J301" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J301" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K301" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11838,7 +12137,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" xml:space="preserve">
       <c r="A302" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11866,8 +12165,9 @@
       <c r="I302" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J302" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J302" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K302" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11876,7 +12176,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" xml:space="preserve">
       <c r="A303" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11904,8 +12204,9 @@
       <c r="I303" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J303" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J303" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K303" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11914,7 +12215,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" xml:space="preserve">
       <c r="A304" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11942,8 +12243,9 @@
       <c r="I304" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J304" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J304" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K304" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11952,7 +12254,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" xml:space="preserve">
       <c r="A305" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -11980,8 +12282,9 @@
       <c r="I305" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J305" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J305" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K305" t="str">
         <v>AM FAIRMOUNT</v>
@@ -11990,7 +12293,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" xml:space="preserve">
       <c r="A306" t="str">
         <v xml:space="preserve">#38: LEVEL 26 SIGNAGE </v>
       </c>
@@ -12018,8 +12321,9 @@
       <c r="I306" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J306" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J306" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K306" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12028,7 +12332,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" xml:space="preserve">
       <c r="A307" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE </v>
       </c>
@@ -12056,8 +12360,9 @@
       <c r="I307" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J307" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J307" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K307" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12066,7 +12371,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" xml:space="preserve">
       <c r="A308" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE </v>
       </c>
@@ -12094,8 +12399,9 @@
       <c r="I308" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J308" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J308" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K308" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12104,7 +12410,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" xml:space="preserve">
       <c r="A309" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE </v>
       </c>
@@ -12132,8 +12438,9 @@
       <c r="I309" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J309" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J309" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K309" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12142,7 +12449,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" xml:space="preserve">
       <c r="A310" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE </v>
       </c>
@@ -12170,8 +12477,9 @@
       <c r="I310" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J310" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J310" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K310" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12180,7 +12488,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" xml:space="preserve">
       <c r="A311" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE </v>
       </c>
@@ -12208,8 +12516,9 @@
       <c r="I311" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J311" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J311" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K311" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12218,7 +12527,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" xml:space="preserve">
       <c r="A312" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE </v>
       </c>
@@ -12246,8 +12555,9 @@
       <c r="I312" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J312" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J312" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K312" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12256,7 +12566,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" xml:space="preserve">
       <c r="A313" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE  </v>
       </c>
@@ -12284,8 +12594,9 @@
       <c r="I313" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J313" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J313" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K313" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12294,7 +12605,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" xml:space="preserve">
       <c r="A314" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE  </v>
       </c>
@@ -12322,8 +12633,9 @@
       <c r="I314" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J314" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J314" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K314" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12332,7 +12644,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" xml:space="preserve">
       <c r="A315" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE  </v>
       </c>
@@ -12360,8 +12672,9 @@
       <c r="I315" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J315" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J315" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K315" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12370,7 +12683,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" xml:space="preserve">
       <c r="A316" t="str">
         <v xml:space="preserve">#39: LEVEL 27 SIGNAGE  </v>
       </c>
@@ -12398,8 +12711,9 @@
       <c r="I316" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J316" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J316" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K316" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12408,7 +12722,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" xml:space="preserve">
       <c r="A317" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12436,8 +12750,9 @@
       <c r="I317" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J317" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J317" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K317" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12446,7 +12761,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" xml:space="preserve">
       <c r="A318" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12474,8 +12789,9 @@
       <c r="I318" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J318" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J318" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K318" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12484,7 +12800,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" xml:space="preserve">
       <c r="A319" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12512,8 +12828,9 @@
       <c r="I319" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J319" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J319" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K319" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12522,7 +12839,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" xml:space="preserve">
       <c r="A320" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12550,8 +12867,9 @@
       <c r="I320" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J320" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J320" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K320" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12560,7 +12878,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" xml:space="preserve">
       <c r="A321" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12588,8 +12906,9 @@
       <c r="I321" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J321" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J321" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K321" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12598,7 +12917,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" xml:space="preserve">
       <c r="A322" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12626,8 +12945,9 @@
       <c r="I322" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J322" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J322" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K322" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12636,7 +12956,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" xml:space="preserve">
       <c r="A323" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12664,8 +12984,9 @@
       <c r="I323" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J323" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J323" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K323" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12674,7 +12995,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" xml:space="preserve">
       <c r="A324" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12702,8 +13023,9 @@
       <c r="I324" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J324" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J324" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K324" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12712,7 +13034,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" xml:space="preserve">
       <c r="A325" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12740,8 +13062,9 @@
       <c r="I325" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J325" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J325" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K325" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12750,7 +13073,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" xml:space="preserve">
       <c r="A326" t="str">
         <v xml:space="preserve">#40: LEVEL 28 SIGNAGE </v>
       </c>
@@ -12778,8 +13101,9 @@
       <c r="I326" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J326" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J326" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K326" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12788,7 +13112,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" xml:space="preserve">
       <c r="A327" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -12816,8 +13140,9 @@
       <c r="I327" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J327" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J327" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K327" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12826,7 +13151,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" xml:space="preserve">
       <c r="A328" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -12854,8 +13179,9 @@
       <c r="I328" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J328" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J328" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K328" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12864,7 +13190,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" xml:space="preserve">
       <c r="A329" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -12892,8 +13218,9 @@
       <c r="I329" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J329" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J329" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K329" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12902,7 +13229,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" xml:space="preserve">
       <c r="A330" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -12930,8 +13257,9 @@
       <c r="I330" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J330" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J330" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K330" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12940,7 +13268,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" xml:space="preserve">
       <c r="A331" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -12968,8 +13296,9 @@
       <c r="I331" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J331" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J331" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K331" t="str">
         <v>AM FAIRMOUNT</v>
@@ -12978,7 +13307,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" xml:space="preserve">
       <c r="A332" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -13006,8 +13335,9 @@
       <c r="I332" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J332" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J332" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K332" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13016,7 +13346,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" xml:space="preserve">
       <c r="A333" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -13044,8 +13374,9 @@
       <c r="I333" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J333" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J333" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K333" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13054,7 +13385,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" xml:space="preserve">
       <c r="A334" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -13082,8 +13413,9 @@
       <c r="I334" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J334" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J334" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K334" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13092,7 +13424,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" xml:space="preserve">
       <c r="A335" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -13120,8 +13452,9 @@
       <c r="I335" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J335" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J335" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K335" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13130,7 +13463,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" xml:space="preserve">
       <c r="A336" t="str">
         <v xml:space="preserve">#41: LEVEL 29 SIGNAGE </v>
       </c>
@@ -13158,8 +13491,9 @@
       <c r="I336" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J336" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J336" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K336" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13168,7 +13502,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" xml:space="preserve">
       <c r="A337" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13196,8 +13530,9 @@
       <c r="I337" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J337" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J337" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K337" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13206,7 +13541,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" xml:space="preserve">
       <c r="A338" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13234,8 +13569,9 @@
       <c r="I338" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J338" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J338" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K338" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13244,7 +13580,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" xml:space="preserve">
       <c r="A339" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13272,8 +13608,9 @@
       <c r="I339" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J339" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J339" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K339" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13282,7 +13619,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" xml:space="preserve">
       <c r="A340" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13310,8 +13647,9 @@
       <c r="I340" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J340" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J340" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K340" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13320,7 +13658,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" xml:space="preserve">
       <c r="A341" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13348,8 +13686,9 @@
       <c r="I341" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J341" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J341" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K341" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13358,7 +13697,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" xml:space="preserve">
       <c r="A342" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13386,8 +13725,9 @@
       <c r="I342" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J342" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J342" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K342" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13396,7 +13736,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" xml:space="preserve">
       <c r="A343" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13424,8 +13764,9 @@
       <c r="I343" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J343" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J343" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K343" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13434,7 +13775,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" xml:space="preserve">
       <c r="A344" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13462,8 +13803,9 @@
       <c r="I344" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J344" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J344" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K344" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13472,7 +13814,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" xml:space="preserve">
       <c r="A345" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13500,8 +13842,9 @@
       <c r="I345" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J345" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J345" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K345" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13510,7 +13853,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" xml:space="preserve">
       <c r="A346" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13538,8 +13881,9 @@
       <c r="I346" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J346" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J346" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K346" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13548,7 +13892,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" xml:space="preserve">
       <c r="A347" t="str">
         <v xml:space="preserve">#42: LEVEL 30 SIGNAGE </v>
       </c>
@@ -13576,8 +13920,9 @@
       <c r="I347" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J347" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J347" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K347" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13586,7 +13931,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" xml:space="preserve">
       <c r="A348" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13614,8 +13959,9 @@
       <c r="I348" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J348" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J348" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K348" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13624,7 +13970,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" xml:space="preserve">
       <c r="A349" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13652,8 +13998,9 @@
       <c r="I349" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J349" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J349" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K349" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13662,7 +14009,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" xml:space="preserve">
       <c r="A350" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13690,8 +14037,9 @@
       <c r="I350" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J350" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J350" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K350" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13700,7 +14048,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" xml:space="preserve">
       <c r="A351" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13728,8 +14076,9 @@
       <c r="I351" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J351" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J351" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K351" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13738,7 +14087,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" xml:space="preserve">
       <c r="A352" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13766,8 +14115,9 @@
       <c r="I352" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J352" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J352" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K352" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13776,7 +14126,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" xml:space="preserve">
       <c r="A353" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13804,8 +14154,9 @@
       <c r="I353" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J353" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J353" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K353" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13814,7 +14165,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" xml:space="preserve">
       <c r="A354" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13842,8 +14193,9 @@
       <c r="I354" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J354" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J354" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K354" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13852,7 +14204,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" xml:space="preserve">
       <c r="A355" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13880,8 +14232,9 @@
       <c r="I355" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J355" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J355" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K355" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13890,7 +14243,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" xml:space="preserve">
       <c r="A356" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13918,8 +14271,9 @@
       <c r="I356" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J356" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J356" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K356" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13928,7 +14282,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" xml:space="preserve">
       <c r="A357" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13956,8 +14310,9 @@
       <c r="I357" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J357" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J357" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K357" t="str">
         <v>AM FAIRMOUNT</v>
@@ -13966,7 +14321,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" xml:space="preserve">
       <c r="A358" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -13994,8 +14349,9 @@
       <c r="I358" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J358" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J358" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K358" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14004,7 +14360,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" xml:space="preserve">
       <c r="A359" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14032,8 +14388,9 @@
       <c r="I359" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J359" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J359" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K359" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14042,7 +14399,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" xml:space="preserve">
       <c r="A360" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14070,8 +14427,9 @@
       <c r="I360" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J360" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J360" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K360" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14080,7 +14438,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" xml:space="preserve">
       <c r="A361" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14108,8 +14466,9 @@
       <c r="I361" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J361" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J361" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K361" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14118,7 +14477,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" xml:space="preserve">
       <c r="A362" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14146,8 +14505,9 @@
       <c r="I362" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J362" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J362" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K362" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14156,7 +14516,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" xml:space="preserve">
       <c r="A363" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14184,8 +14544,9 @@
       <c r="I363" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J363" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J363" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K363" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14194,7 +14555,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" xml:space="preserve">
       <c r="A364" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14222,8 +14583,9 @@
       <c r="I364" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J364" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J364" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K364" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14232,7 +14594,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" xml:space="preserve">
       <c r="A365" t="str">
         <v xml:space="preserve">#43: LEVEL 31 SIGNAGE </v>
       </c>
@@ -14260,8 +14622,9 @@
       <c r="I365" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J365" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J365" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K365" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14270,7 +14633,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" xml:space="preserve">
       <c r="A366" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14298,8 +14661,9 @@
       <c r="I366" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J366" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J366" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K366" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14308,7 +14672,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" xml:space="preserve">
       <c r="A367" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14336,8 +14700,9 @@
       <c r="I367" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J367" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J367" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K367" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14346,7 +14711,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" xml:space="preserve">
       <c r="A368" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14374,8 +14739,9 @@
       <c r="I368" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J368" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J368" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K368" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14384,7 +14750,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" xml:space="preserve">
       <c r="A369" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14412,8 +14778,9 @@
       <c r="I369" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J369" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J369" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K369" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14422,7 +14789,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" xml:space="preserve">
       <c r="A370" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14450,8 +14817,9 @@
       <c r="I370" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J370" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J370" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K370" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14460,7 +14828,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" xml:space="preserve">
       <c r="A371" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14488,8 +14856,9 @@
       <c r="I371" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J371" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J371" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K371" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14498,7 +14867,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" xml:space="preserve">
       <c r="A372" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14526,8 +14895,9 @@
       <c r="I372" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J372" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J372" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K372" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14536,7 +14906,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" xml:space="preserve">
       <c r="A373" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14564,8 +14934,9 @@
       <c r="I373" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J373" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J373" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K373" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14574,7 +14945,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" xml:space="preserve">
       <c r="A374" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14602,8 +14973,9 @@
       <c r="I374" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J374" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J374" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K374" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14612,7 +14984,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" xml:space="preserve">
       <c r="A375" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14640,8 +15012,9 @@
       <c r="I375" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J375" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J375" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K375" t="str">
         <v>AM FAIRMOUNT</v>
@@ -14650,7 +15023,7 @@
         <v>2211AM01S Fairmount Signage REV 1.xlsx</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" xml:space="preserve">
       <c r="A376" t="str">
         <v xml:space="preserve">#44: AMENITY SIGNAGE </v>
       </c>
@@ -14678,8 +15051,9 @@
       <c r="I376" t="str">
         <v>2211AM01S</v>
       </c>
-      <c r="J376" t="str">
-        <v>05.22.23 REV 1</v>
+      <c r="J376" t="str" xml:space="preserve">
+        <v xml:space="preserve">05.22.23 REV 1
+</v>
       </c>
       <c r="K376" t="str">
         <v>AM FAIRMOUNT</v>
